--- a/04_DESIGN_TABLES/DesignTable_6500L.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_6500L.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -943,6 +943,33 @@
           <t>6500-L-04-04-FG</t>
         </is>
       </c>
+      <c r="B9" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.816</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.5629999999999999</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.438</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.172</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.172</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.4375</v>
+      </c>
       <c r="K9" t="inlineStr">
         <is>
           <t>6500-L-04-04-FG</t>
@@ -950,17 +977,17 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6500-L-04-04 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
+          <t>OMi WebsitePartsInfo2026.xlsx Items row 1936 (OMi first, user decision 2026-09-25): M = L 1, M9 = M 2 (crossing to the swivel-nut face), M12 = M 1 (crossing to the nose tip), Y = Hex Flat, CHEX = Nut Hex 1, D1 / D2 = Side 1 / Side 2 ID - column meaning from the Brennan TFA catalog p34 drawing letters (M / M6 / M4 / Y FLATS / C HEX / B1 / B2 DRILL, OMi = catalog 5/5); OMi and Brennan are ONE source -&gt; ASSUMED; male JIC end VERIFIED (MS33656J) | OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6500-L-04-04 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied ; Brennan 3D files give SHAPE only here (user 2026-10-08: "shape is fine"; no size from Brennan alone): the forged swivel hex arm runs on to the swivel end of the same size (BRENNAN_6500-L-08-08-FG; its length through the swivel end-library constant SW2_BODYS); the sizes of the part are OMi's</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6500-L-04-04 dims are NOT assumed; confirm before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6500-L-04-04 dims are NOT assumed; confirm before modelling | FOLDS 2026-10-02: filled from OMi Items row 1936; Brennan TFA catalog p34 (same source) differs only in the last printed digit (the catalog cuts OMi M 1 to 2 decimals, QA_Log #158; 9/16 = 0.5625 printed 0.562 / 0.563): M12 OMi 1.816 vs catalog 1.81; CHEX OMi 0.563 vs catalog 0.562</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -980,6 +1007,33 @@
           <t>6500-L-06-06-FG</t>
         </is>
       </c>
+      <c r="B10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.165</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.6879999999999999</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.5625</v>
+      </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>6500-L-06-06-FG</t>
@@ -987,17 +1041,17 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6500-L-06-06 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
+          <t>OMi WebsitePartsInfo2026.xlsx Items row 1937 (OMi first, user decision 2026-09-25): M = L 1, M9 = M 2 (crossing to the swivel-nut face), M12 = M 1 (crossing to the nose tip), Y = Hex Flat, CHEX = Nut Hex 1, D1 / D2 = Side 1 / Side 2 ID - column meaning from the Brennan TFA catalog p34 drawing letters (M / M6 / M4 / Y FLATS / C HEX / B1 / B2 DRILL, OMi = catalog 5/5); OMi and Brennan are ONE source -&gt; ASSUMED; male JIC end VERIFIED (MS33656J) | OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6500-L-06-06 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied ; Brennan 3D files give SHAPE only here (user 2026-10-08: "shape is fine"; no size from Brennan alone): the forged swivel hex arm runs on to the swivel end of the same size (BRENNAN_6500-L-08-08-FG; its length through the swivel end-library constant SW2_BODYS); the sizes of the part are OMi's</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6500-L-06-06 dims are NOT assumed; confirm before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6500-L-06-06 dims are NOT assumed; confirm before modelling | FOLDS 2026-10-02: filled from OMi Items row 1937; Brennan TFA catalog p34 (same source) differs only in the last printed digit (the catalog cuts OMi M 1 to 2 decimals, QA_Log #158; 9/16 = 0.5625 printed 0.562 / 0.563): M12 OMi 2.165 vs catalog 2.16</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1017,6 +1071,33 @@
           <t>6500-L-08-08-FG</t>
         </is>
       </c>
+      <c r="B11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.388</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.75</v>
+      </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>6500-L-08-08-FG</t>
@@ -1024,17 +1105,17 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6500-L-08-08 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
+          <t>OMi WebsitePartsInfo2026.xlsx Items row 1938 (OMi first, user decision 2026-09-25): M = L 1, M9 = M 2 (crossing to the swivel-nut face), M12 = M 1 (crossing to the nose tip), Y = Hex Flat, CHEX = Nut Hex 1, D1 / D2 = Side 1 / Side 2 ID - column meaning from the Brennan TFA catalog p34 drawing letters (M / M6 / M4 / Y FLATS / C HEX / B1 / B2 DRILL, OMi = catalog 5/5); OMi and Brennan are ONE source -&gt; ASSUMED; male JIC end VERIFIED (MS33656J) | OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6500-L-08-08 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied ; Brennan 3D files give SHAPE only here (user 2026-10-08: "shape is fine"; no size from Brennan alone): the forged swivel hex arm runs on to the swivel end of the same size (BRENNAN_6500-L-08-08-FG; its length through the swivel end-library constant SW2_BODYS); the sizes of the part are OMi's</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6500-L-08-08 dims are NOT assumed; confirm before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6500-L-08-08 dims are NOT assumed; confirm before modelling | FOLDS 2026-10-02: filled from OMi Items row 1938; Brennan TFA catalog p34 (same source) differs only in the last printed digit (the catalog cuts OMi M 1 to 2 decimals, QA_Log #158; 9/16 = 0.5625 printed 0.562 / 0.563): M12 OMi 2.388 vs catalog 2.38; Brennan 6500-L-08-08-FG STEP (pilot, elbow90.py + swiv.py): M 1.2501; M9 2.8101; M12 2.3801; Y 0.75; CHEX 0.875; D1 0.391; D2 0.391 - equal to OMi except the nose tip M12 (STEP 2.3801 = nut face 2.8101 - 0.43; OMi 2.388, +0.008, the same offset as OMi / Air-Way 0.96 vs the 6500-08-08-FG STEP 0.95) - built to OMi</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1054,6 +1135,33 @@
           <t>6500-L-12-12-FG</t>
         </is>
       </c>
+      <c r="B12" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="C12" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="D12" t="n">
+        <v>3.738</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.062</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.0625</v>
+      </c>
       <c r="K12" t="inlineStr">
         <is>
           <t>6500-L-12-12-FG</t>
@@ -1061,17 +1169,17 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6500-L-12-12 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
+          <t>OMi WebsitePartsInfo2026.xlsx Items row 1939 (OMi first, user decision 2026-09-25): M = L 1, M9 = M 2 (crossing to the swivel-nut face), M12 = M 1 (crossing to the nose tip), Y = Hex Flat, CHEX = Nut Hex 1, D1 / D2 = Side 1 / Side 2 ID - column meaning from the Brennan TFA catalog p34 drawing letters (M / M6 / M4 / Y FLATS / C HEX / B1 / B2 DRILL, OMi = catalog 5/5); OMi and Brennan are ONE source -&gt; ASSUMED; male JIC end VERIFIED (MS33656J) | OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6500-L-12-12 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied ; Brennan 3D files give SHAPE only here (user 2026-10-08: "shape is fine"; no size from Brennan alone): the forged swivel hex arm runs on to the swivel end of the same size (BRENNAN_6500-L-08-08-FG; its length through the swivel end-library constant SW2_BODYS); the sizes of the part are OMi's</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6500-L-12-12 dims are NOT assumed; confirm before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6500-L-12-12 dims are NOT assumed; confirm before modelling | FOLDS 2026-10-02: filled from OMi Items row 1939; Brennan TFA catalog p34 (same source) differs only in the last printed digit (the catalog cuts OMi M 1 to 2 decimals, QA_Log #158; 9/16 = 0.5625 printed 0.562 / 0.563): M12 OMi 3.738 vs catalog 3.73</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1091,6 +1199,33 @@
           <t>6500-L-16-16-FG</t>
         </is>
       </c>
+      <c r="B13" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="C13" t="n">
+        <v>5</v>
+      </c>
+      <c r="D13" t="n">
+        <v>4.406</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.844</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.844</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.3125</v>
+      </c>
       <c r="K13" t="inlineStr">
         <is>
           <t>6500-L-16-16-FG</t>
@@ -1098,17 +1233,17 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6500-L-16-16 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
+          <t>OMi WebsitePartsInfo2026.xlsx Items row 1940 (OMi first, user decision 2026-09-25): M = L 1, M9 = M 2 (crossing to the swivel-nut face), M12 = M 1 (crossing to the nose tip), Y = Hex Flat, CHEX = Nut Hex 1, D1 / D2 = Side 1 / Side 2 ID - column meaning from the Brennan TFA catalog p34 drawing letters (M / M6 / M4 / Y FLATS / C HEX / B1 / B2 DRILL, OMi = catalog 5/5); OMi and Brennan are ONE source -&gt; ASSUMED; male JIC end VERIFIED (MS33656J) | OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6500-L-16-16 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied ; Brennan 3D files give SHAPE only here (user 2026-10-08: "shape is fine"; no size from Brennan alone): the forged swivel hex arm runs on to the swivel end of the same size (BRENNAN_6500-L-08-08-FG; its length through the swivel end-library constant SW2_BODYS); the sizes of the part are OMi's</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6500-L-16-16 dims are NOT assumed; confirm before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6500-L-16-16 dims are NOT assumed; confirm before modelling | FOLDS 2026-10-02: filled from OMi Items row 1940; Brennan TFA catalog p34 (same source) differs only in the last printed digit (the catalog cuts OMi M 1 to 2 decimals, QA_Log #158; 9/16 = 0.5625 printed 0.562 / 0.563): M12 OMi 4.406 vs catalog 4.40</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
